--- a/gestion-mg-hote/MG_Hote_Gestion.xlsx
+++ b/gestion-mg-hote/MG_Hote_Gestion.xlsx
@@ -21,7 +21,7 @@
     <sheet name="Paramètres" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="Liste_Biens">Paramètres!$B$3:$B$12</definedName>
+    <definedName name="Liste_Biens">Biens!$A$5:$A$14</definedName>
     <definedName name="Liste_BiensGeneral">Paramètres!$C$3:$C$13</definedName>
     <definedName name="Liste_Plateformes">Paramètres!$D$3:$D$5</definedName>
     <definedName name="Liste_StatutResa">Paramètres!$E$3:$E$6</definedName>
@@ -1503,7 +1503,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="C7B6"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="C7B6"/>
   <mergeCells count="28">
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="F10:G10"/>
@@ -1880,7 +1880,7 @@
     <row r="34"/>
     <row r="35"/>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="C7B6"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="C7B6"/>
   <mergeCells count="31">
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="G21:H21"/>
@@ -2213,7 +2213,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="C7B6"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="C7B6"/>
   <mergeCells count="42">
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A8:D8"/>
@@ -2365,15 +2365,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="38" t="inlineStr">
-        <is>
-          <t>Bien 1</t>
-        </is>
-      </c>
-      <c r="C3" s="38" t="inlineStr">
-        <is>
-          <t>Bien 1</t>
-        </is>
+      <c r="B3" s="38">
+        <f>IF(Biens!A5="","",Biens!A5)</f>
+        <v/>
+      </c>
+      <c r="C3" s="38">
+        <f>IF(Biens!A5="","",Biens!A5)</f>
+        <v/>
       </c>
       <c r="D3" s="38" t="inlineStr">
         <is>
@@ -2432,15 +2430,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="38" t="inlineStr">
-        <is>
-          <t>Bien 2</t>
-        </is>
-      </c>
-      <c r="C4" s="38" t="inlineStr">
-        <is>
-          <t>Bien 2</t>
-        </is>
+      <c r="B4" s="38">
+        <f>IF(Biens!A6="","",Biens!A6)</f>
+        <v/>
+      </c>
+      <c r="C4" s="38">
+        <f>IF(Biens!A6="","",Biens!A6)</f>
+        <v/>
       </c>
       <c r="D4" s="38" t="inlineStr">
         <is>
@@ -2499,15 +2495,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="38" t="inlineStr">
-        <is>
-          <t>Bien 3</t>
-        </is>
-      </c>
-      <c r="C5" s="38" t="inlineStr">
-        <is>
-          <t>Bien 3</t>
-        </is>
+      <c r="B5" s="38">
+        <f>IF(Biens!A7="","",Biens!A7)</f>
+        <v/>
+      </c>
+      <c r="C5" s="38">
+        <f>IF(Biens!A7="","",Biens!A7)</f>
+        <v/>
       </c>
       <c r="D5" s="38" t="inlineStr">
         <is>
@@ -2551,15 +2545,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="38" t="inlineStr">
-        <is>
-          <t>Bien 4</t>
-        </is>
-      </c>
-      <c r="C6" s="38" t="inlineStr">
-        <is>
-          <t>Bien 4</t>
-        </is>
+      <c r="B6" s="38">
+        <f>IF(Biens!A8="","",Biens!A8)</f>
+        <v/>
+      </c>
+      <c r="C6" s="38">
+        <f>IF(Biens!A8="","",Biens!A8)</f>
+        <v/>
       </c>
       <c r="E6" s="38" t="inlineStr">
         <is>
@@ -2583,15 +2575,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="38" t="inlineStr">
-        <is>
-          <t>Bien 5</t>
-        </is>
-      </c>
-      <c r="C7" s="38" t="inlineStr">
-        <is>
-          <t>Bien 5</t>
-        </is>
+      <c r="B7" s="38">
+        <f>IF(Biens!A9="","",Biens!A9)</f>
+        <v/>
+      </c>
+      <c r="C7" s="38">
+        <f>IF(Biens!A9="","",Biens!A9)</f>
+        <v/>
       </c>
       <c r="L7" s="38" t="inlineStr">
         <is>
@@ -2605,15 +2595,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="38" t="inlineStr">
-        <is>
-          <t>Bien 6</t>
-        </is>
-      </c>
-      <c r="C8" s="38" t="inlineStr">
-        <is>
-          <t>Bien 6</t>
-        </is>
+      <c r="B8" s="38">
+        <f>IF(Biens!A10="","",Biens!A10)</f>
+        <v/>
+      </c>
+      <c r="C8" s="38">
+        <f>IF(Biens!A10="","",Biens!A10)</f>
+        <v/>
       </c>
       <c r="L8" s="38" t="inlineStr">
         <is>
@@ -2622,15 +2610,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="38" t="inlineStr">
-        <is>
-          <t>Bien 7</t>
-        </is>
-      </c>
-      <c r="C9" s="38" t="inlineStr">
-        <is>
-          <t>Bien 7</t>
-        </is>
+      <c r="B9" s="38">
+        <f>IF(Biens!A11="","",Biens!A11)</f>
+        <v/>
+      </c>
+      <c r="C9" s="38">
+        <f>IF(Biens!A11="","",Biens!A11)</f>
+        <v/>
       </c>
       <c r="L9" s="38" t="inlineStr">
         <is>
@@ -2639,15 +2625,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="38" t="inlineStr">
-        <is>
-          <t>Bien 8</t>
-        </is>
-      </c>
-      <c r="C10" s="38" t="inlineStr">
-        <is>
-          <t>Bien 8</t>
-        </is>
+      <c r="B10" s="38">
+        <f>IF(Biens!A12="","",Biens!A12)</f>
+        <v/>
+      </c>
+      <c r="C10" s="38">
+        <f>IF(Biens!A12="","",Biens!A12)</f>
+        <v/>
       </c>
       <c r="L10" s="38" t="inlineStr">
         <is>
@@ -2656,15 +2640,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="38" t="inlineStr">
-        <is>
-          <t>Bien 9</t>
-        </is>
-      </c>
-      <c r="C11" s="38" t="inlineStr">
-        <is>
-          <t>Bien 9</t>
-        </is>
+      <c r="B11" s="38">
+        <f>IF(Biens!A13="","",Biens!A13)</f>
+        <v/>
+      </c>
+      <c r="C11" s="38">
+        <f>IF(Biens!A13="","",Biens!A13)</f>
+        <v/>
       </c>
       <c r="L11" s="38" t="inlineStr">
         <is>
@@ -2673,15 +2655,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="38" t="inlineStr">
-        <is>
-          <t>Bien 10</t>
-        </is>
-      </c>
-      <c r="C12" s="38" t="inlineStr">
-        <is>
-          <t>Bien 10</t>
-        </is>
+      <c r="B12" s="38">
+        <f>IF(Biens!A14="","",Biens!A14)</f>
+        <v/>
+      </c>
+      <c r="C12" s="38">
+        <f>IF(Biens!A14="","",Biens!A14)</f>
+        <v/>
       </c>
       <c r="L12" s="38" t="inlineStr">
         <is>
@@ -2702,7 +2682,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="C7B6"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="C7B6"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -3095,7 +3075,7 @@
     <row r="77"/>
     <row r="78"/>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="C7B6"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="C7B6"/>
   <mergeCells count="44">
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A43:H45"/>
@@ -11311,7 +11291,7 @@
       <c r="T204" s="26" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0" password="C7B6"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="C7B6"/>
   <autoFilter ref="A4:T204"/>
   <mergeCells count="4">
     <mergeCell ref="A1:B2"/>
@@ -11617,16 +11597,13 @@
       <c r="L14" s="26" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0" password="C7B6"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="C7B6"/>
   <mergeCells count="3">
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C2:L2"/>
     <mergeCell ref="C1:L1"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation sqref="A5:A14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Liste_Biens</formula1>
-    </dataValidation>
+  <dataValidations count="2">
     <dataValidation sqref="B5:B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Liste_TypeBien</formula1>
     </dataValidation>
@@ -11885,7 +11862,7 @@
       <c r="J14" s="26" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0" password="C7B6"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="C7B6"/>
   <mergeCells count="3">
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:J1"/>
@@ -16500,7 +16477,7 @@
       <c r="J304" s="26" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0" password="C7B6"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="C7B6"/>
   <autoFilter ref="A4:J304"/>
   <mergeCells count="3">
     <mergeCell ref="A1:B2"/>
@@ -17358,7 +17335,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="C7B6"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="C7B6"/>
   <mergeCells count="4">
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A3:D3"/>
@@ -19433,7 +19410,7 @@
       <c r="K154" s="26" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0" password="C7B6"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="C7B6"/>
   <autoFilter ref="A4:K154"/>
   <mergeCells count="3">
     <mergeCell ref="A1:B2"/>
@@ -20756,7 +20733,7 @@
       <c r="J104" s="26" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0" password="C7B6"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="C7B6"/>
   <autoFilter ref="A4:J104"/>
   <mergeCells count="3">
     <mergeCell ref="A1:B2"/>

--- a/gestion-mg-hote/MG_Hote_Gestion.xlsx
+++ b/gestion-mg-hote/MG_Hote_Gestion.xlsx
@@ -39,7 +39,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="6">'Synthèse Mensuelle'!$A$1:$N$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Ménage'!$A$4:$K$154</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Maintenance'!$A$4:$J$104</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'Facture Propriétaire'!$A$1:$H$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'Facture Propriétaire'!$A$1:$H$37</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="10">'Rapport Mensuel'!$A$1:$F$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1563,7 +1563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1720,11 +1720,11 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="39" t="inlineStr">
         <is>
-          <t>Total recettes brutes (plateformes)</t>
+          <t>Chiffre d'affaires brut des réservations (Prix total)</t>
         </is>
       </c>
       <c r="G15" s="32">
-        <f>SUMIFS('Journal Financier'!$F$5:$F$304,'Journal Financier'!$B$5:$B$304,$G$5,'Journal Financier'!$C$5:$C$304,"Recette",'Journal Financier'!$A$5:$A$304,"&gt;="&amp;$C$6,'Journal Financier'!$A$5:$A$304,"&lt;="&amp;$G$6)</f>
+        <f>SUMIFS(Réservations!$L$5:$L$204,Réservations!$B$5:$B$204,$G$5,Réservations!$G$5:$G$204,"&gt;="&amp;$C$6,Réservations!$G$5:$G$204,"&lt;="&amp;$G$6,Réservations!$Q$5:$Q$204,"&lt;&gt;Annulée")</f>
         <v/>
       </c>
       <c r="H15" s="40" t="n"/>
@@ -1732,23 +1732,23 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="38" t="inlineStr">
         <is>
-          <t>Taux de commission MG Hôte</t>
-        </is>
-      </c>
-      <c r="G16" s="34">
-        <f>IFERROR(INDEX(Biens!$I$5:$I$14,MATCH($G$5,Biens!$A$5:$A$14,0)),0)</f>
+          <t>Frais plateforme (Airbnb / Booking)</t>
+        </is>
+      </c>
+      <c r="G16" s="31">
+        <f>SUMIFS(Réservations!$M$5:$M$204,Réservations!$B$5:$B$204,$G$5,Réservations!$G$5:$G$204,"&gt;="&amp;$C$6,Réservations!$G$5:$G$204,"&lt;="&amp;$G$6,Réservations!$Q$5:$Q$204,"&lt;&gt;Annulée")</f>
         <v/>
       </c>
       <c r="H16" s="40" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="38" t="inlineStr">
-        <is>
-          <t>Montant commission MG Hôte</t>
-        </is>
-      </c>
-      <c r="G17" s="31">
-        <f>G15*G16</f>
+      <c r="A17" s="39" t="inlineStr">
+        <is>
+          <t>Montant net après frais plateforme</t>
+        </is>
+      </c>
+      <c r="G17" s="32">
+        <f>SUMIFS(Réservations!$N$5:$N$204,Réservations!$B$5:$B$204,$G$5,Réservations!$G$5:$G$204,"&gt;="&amp;$C$6,Réservations!$G$5:$G$204,"&lt;="&amp;$G$6,Réservations!$Q$5:$Q$204,"&lt;&gt;Annulée")</f>
         <v/>
       </c>
       <c r="H17" s="40" t="n"/>
@@ -1756,11 +1756,11 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="38" t="inlineStr">
         <is>
-          <t>Charges refacturées au propriétaire :</t>
-        </is>
-      </c>
-      <c r="G18" s="28">
-        <f>""</f>
+          <t>Taux de commission MG Hôte</t>
+        </is>
+      </c>
+      <c r="G18" s="34">
+        <f>IFERROR(INDEX(Biens!$I$5:$I$14,MATCH($G$5,Biens!$A$5:$A$14,0)),0)</f>
         <v/>
       </c>
       <c r="H18" s="40" t="n"/>
@@ -1768,11 +1768,11 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Maintenance</t>
+          <t>Montant commission MG Hôte</t>
         </is>
       </c>
       <c r="G19" s="31">
-        <f>SUMIFS('Journal Financier'!$F$5:$F$304,'Journal Financier'!$B$5:$B$304,$G$5,'Journal Financier'!$C$5:$C$304,"Dépense",'Journal Financier'!$D$5:$D$304,"Maintenance",'Journal Financier'!$A$5:$A$304,"&gt;="&amp;$C$6,'Journal Financier'!$A$5:$A$304,"&lt;="&amp;$G$6)</f>
+        <f>SUMIFS(Réservations!$O$5:$O$204,Réservations!$B$5:$B$204,$G$5,Réservations!$G$5:$G$204,"&gt;="&amp;$C$6,Réservations!$G$5:$G$204,"&lt;="&amp;$G$6,Réservations!$Q$5:$Q$204,"&lt;&gt;Annulée")</f>
         <v/>
       </c>
       <c r="H19" s="40" t="n"/>
@@ -1780,11 +1780,11 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Consommables</t>
-        </is>
-      </c>
-      <c r="G20" s="31">
-        <f>SUMIFS('Journal Financier'!$F$5:$F$304,'Journal Financier'!$B$5:$B$304,$G$5,'Journal Financier'!$C$5:$C$304,"Dépense",'Journal Financier'!$D$5:$D$304,"Consommables",'Journal Financier'!$A$5:$A$304,"&gt;="&amp;$C$6,'Journal Financier'!$A$5:$A$304,"&lt;="&amp;$G$6)</f>
+          <t>Charges refacturées au propriétaire :</t>
+        </is>
+      </c>
+      <c r="G20" s="28">
+        <f>""</f>
         <v/>
       </c>
       <c r="H20" s="40" t="n"/>
@@ -1792,11 +1792,11 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Électricité</t>
+          <t xml:space="preserve">      Maintenance</t>
         </is>
       </c>
       <c r="G21" s="31">
-        <f>SUMIFS('Journal Financier'!$F$5:$F$304,'Journal Financier'!$B$5:$B$304,$G$5,'Journal Financier'!$C$5:$C$304,"Dépense",'Journal Financier'!$D$5:$D$304,"Électricité",'Journal Financier'!$A$5:$A$304,"&gt;="&amp;$C$6,'Journal Financier'!$A$5:$A$304,"&lt;="&amp;$G$6)</f>
+        <f>SUMIFS('Journal Financier'!$F$5:$F$304,'Journal Financier'!$B$5:$B$304,$G$5,'Journal Financier'!$C$5:$C$304,"Dépense",'Journal Financier'!$D$5:$D$304,"Maintenance",'Journal Financier'!$A$5:$A$304,"&gt;="&amp;$C$6,'Journal Financier'!$A$5:$A$304,"&lt;="&amp;$G$6)</f>
         <v/>
       </c>
       <c r="H21" s="40" t="n"/>
@@ -1804,11 +1804,11 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Eau</t>
+          <t xml:space="preserve">      Consommables</t>
         </is>
       </c>
       <c r="G22" s="31">
-        <f>SUMIFS('Journal Financier'!$F$5:$F$304,'Journal Financier'!$B$5:$B$304,$G$5,'Journal Financier'!$C$5:$C$304,"Dépense",'Journal Financier'!$D$5:$D$304,"Eau",'Journal Financier'!$A$5:$A$304,"&gt;="&amp;$C$6,'Journal Financier'!$A$5:$A$304,"&lt;="&amp;$G$6)</f>
+        <f>SUMIFS('Journal Financier'!$F$5:$F$304,'Journal Financier'!$B$5:$B$304,$G$5,'Journal Financier'!$C$5:$C$304,"Dépense",'Journal Financier'!$D$5:$D$304,"Consommables",'Journal Financier'!$A$5:$A$304,"&gt;="&amp;$C$6,'Journal Financier'!$A$5:$A$304,"&lt;="&amp;$G$6)</f>
         <v/>
       </c>
       <c r="H22" s="40" t="n"/>
@@ -1816,76 +1816,103 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="38" t="inlineStr">
         <is>
+          <t xml:space="preserve">      Électricité</t>
+        </is>
+      </c>
+      <c r="G23" s="31">
+        <f>SUMIFS('Journal Financier'!$F$5:$F$304,'Journal Financier'!$B$5:$B$304,$G$5,'Journal Financier'!$C$5:$C$304,"Dépense",'Journal Financier'!$D$5:$D$304,"Électricité",'Journal Financier'!$A$5:$A$304,"&gt;="&amp;$C$6,'Journal Financier'!$A$5:$A$304,"&lt;="&amp;$G$6)</f>
+        <v/>
+      </c>
+      <c r="H23" s="40" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Eau</t>
+        </is>
+      </c>
+      <c r="G24" s="31">
+        <f>SUMIFS('Journal Financier'!$F$5:$F$304,'Journal Financier'!$B$5:$B$304,$G$5,'Journal Financier'!$C$5:$C$304,"Dépense",'Journal Financier'!$D$5:$D$304,"Eau",'Journal Financier'!$A$5:$A$304,"&gt;="&amp;$C$6,'Journal Financier'!$A$5:$A$304,"&lt;="&amp;$G$6)</f>
+        <v/>
+      </c>
+      <c r="H24" s="40" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="38" t="inlineStr">
+        <is>
           <t xml:space="preserve">      Publicité</t>
         </is>
       </c>
-      <c r="G23" s="31">
+      <c r="G25" s="31">
         <f>SUMIFS('Journal Financier'!$F$5:$F$304,'Journal Financier'!$B$5:$B$304,$G$5,'Journal Financier'!$C$5:$C$304,"Dépense",'Journal Financier'!$D$5:$D$304,"Publicité",'Journal Financier'!$A$5:$A$304,"&gt;="&amp;$C$6,'Journal Financier'!$A$5:$A$304,"&lt;="&amp;$G$6)</f>
         <v/>
       </c>
-      <c r="H23" s="40" t="n"/>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="39" t="inlineStr">
+      <c r="H25" s="40" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="39" t="inlineStr">
         <is>
           <t>Sous-total charges refacturées</t>
         </is>
       </c>
-      <c r="G24" s="32">
-        <f>SUM(G19:G23)</f>
-        <v/>
-      </c>
-      <c r="H24" s="40" t="n"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="41" t="inlineStr">
+      <c r="G26" s="32">
+        <f>SUM(G21:G25)</f>
+        <v/>
+      </c>
+      <c r="H26" s="40" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="41" t="inlineStr">
         <is>
           <t>MONTANT NET À VERSER AU PROPRIÉTAIRE</t>
         </is>
       </c>
-      <c r="G25" s="42">
-        <f>G15-G17-G24</f>
-        <v/>
-      </c>
-      <c r="H25" s="40" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="21" t="inlineStr">
+      <c r="G27" s="42">
+        <f>G17-G19-G26</f>
+        <v/>
+      </c>
+      <c r="H27" s="40" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>Fait à ______________________, le</t>
         </is>
       </c>
-      <c r="D28" s="43">
+      <c r="D30" s="43">
         <f>TODAY()</f>
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="44" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="44" t="inlineStr">
         <is>
           <t>Signature MG Hôte</t>
         </is>
       </c>
-      <c r="E31" s="44" t="inlineStr">
+      <c r="E33" s="44" t="inlineStr">
         <is>
           <t>Signature Propriétaire</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="45" t="n"/>
-      <c r="E32" s="45" t="n"/>
-    </row>
-    <row r="33"/>
-    <row r="34"/>
+    <row r="34">
+      <c r="A34" s="45" t="n"/>
+      <c r="E34" s="45" t="n"/>
+    </row>
     <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="C7B6"/>
-  <mergeCells count="31">
+  <mergeCells count="35">
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="G21:H21"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="G27:H27"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="G23:H23"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="C2:H2"/>
@@ -1894,9 +1921,9 @@
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A17:F17"/>
+    <mergeCell ref="E34:H37"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="G18:H18"/>
-    <mergeCell ref="A32:D35"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="G15:H15"/>
@@ -1904,11 +1931,12 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A15:F15"/>
-    <mergeCell ref="E32:H35"/>
+    <mergeCell ref="G26:H26"/>
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="G25:H25"/>
+    <mergeCell ref="A34:D37"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="G22:H22"/>
     <mergeCell ref="A25:F25"/>

--- a/gestion-mg-hote/MG_Hote_Gestion.xlsx
+++ b/gestion-mg-hote/MG_Hote_Gestion.xlsx
@@ -892,6 +892,21 @@
     <author>MG Hôte</author>
   </authors>
   <commentList>
+    <comment ref="C6" authorId="0" shapeId="0">
+      <text>
+        <t>Pré-rempli sur le mois en cours. Remplacez par une vraie date (pas une formule) pour figer la période de cette facture.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>MG Hôte</author>
+  </authors>
+  <commentList>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
         <t>Saisissez le 1er jour du mois à analyser (ex: 01/07/2026). Toutes les données ci-dessous se recalculent automatiquement.</t>
@@ -1637,13 +1652,19 @@
           <t>Période — du</t>
         </is>
       </c>
-      <c r="C6" s="27" t="n"/>
+      <c r="C6" s="27">
+        <f>EOMONTH(TODAY(),-1)+1</f>
+        <v/>
+      </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
           <t>au</t>
         </is>
       </c>
-      <c r="G6" s="27" t="n"/>
+      <c r="G6" s="27">
+        <f>EOMONTH(TODAY(),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -1724,7 +1745,7 @@
         </is>
       </c>
       <c r="G15" s="32">
-        <f>SUMIFS(Réservations!$L$5:$L$204,Réservations!$B$5:$B$204,$G$5,Réservations!$G$5:$G$204,"&gt;="&amp;$C$6,Réservations!$G$5:$G$204,"&lt;="&amp;$G$6,Réservations!$Q$5:$Q$204,"&lt;&gt;Annulée")</f>
+        <f>SUMIFS(Réservations!$L$5:$L$204,Réservations!$B$5:$B$204,$G$5,Réservations!$G$5:$G$204,"&gt;="&amp;IF($C$6="",0,$C$6),Réservations!$G$5:$G$204,"&lt;="&amp;IF($G$6="",DATE(2099,12,31),$G$6),Réservations!$Q$5:$Q$204,"&lt;&gt;Annulée")</f>
         <v/>
       </c>
       <c r="H15" s="40" t="n"/>
@@ -1736,7 +1757,7 @@
         </is>
       </c>
       <c r="G16" s="31">
-        <f>SUMIFS(Réservations!$M$5:$M$204,Réservations!$B$5:$B$204,$G$5,Réservations!$G$5:$G$204,"&gt;="&amp;$C$6,Réservations!$G$5:$G$204,"&lt;="&amp;$G$6,Réservations!$Q$5:$Q$204,"&lt;&gt;Annulée")</f>
+        <f>SUMIFS(Réservations!$M$5:$M$204,Réservations!$B$5:$B$204,$G$5,Réservations!$G$5:$G$204,"&gt;="&amp;IF($C$6="",0,$C$6),Réservations!$G$5:$G$204,"&lt;="&amp;IF($G$6="",DATE(2099,12,31),$G$6),Réservations!$Q$5:$Q$204,"&lt;&gt;Annulée")</f>
         <v/>
       </c>
       <c r="H16" s="40" t="n"/>
@@ -1748,7 +1769,7 @@
         </is>
       </c>
       <c r="G17" s="32">
-        <f>SUMIFS(Réservations!$N$5:$N$204,Réservations!$B$5:$B$204,$G$5,Réservations!$G$5:$G$204,"&gt;="&amp;$C$6,Réservations!$G$5:$G$204,"&lt;="&amp;$G$6,Réservations!$Q$5:$Q$204,"&lt;&gt;Annulée")</f>
+        <f>SUMIFS(Réservations!$N$5:$N$204,Réservations!$B$5:$B$204,$G$5,Réservations!$G$5:$G$204,"&gt;="&amp;IF($C$6="",0,$C$6),Réservations!$G$5:$G$204,"&lt;="&amp;IF($G$6="",DATE(2099,12,31),$G$6),Réservations!$Q$5:$Q$204,"&lt;&gt;Annulée")</f>
         <v/>
       </c>
       <c r="H17" s="40" t="n"/>
@@ -1772,7 +1793,7 @@
         </is>
       </c>
       <c r="G19" s="31">
-        <f>SUMIFS(Réservations!$O$5:$O$204,Réservations!$B$5:$B$204,$G$5,Réservations!$G$5:$G$204,"&gt;="&amp;$C$6,Réservations!$G$5:$G$204,"&lt;="&amp;$G$6,Réservations!$Q$5:$Q$204,"&lt;&gt;Annulée")</f>
+        <f>SUMIFS(Réservations!$O$5:$O$204,Réservations!$B$5:$B$204,$G$5,Réservations!$G$5:$G$204,"&gt;="&amp;IF($C$6="",0,$C$6),Réservations!$G$5:$G$204,"&lt;="&amp;IF($G$6="",DATE(2099,12,31),$G$6),Réservations!$Q$5:$Q$204,"&lt;&gt;Annulée")</f>
         <v/>
       </c>
       <c r="H19" s="40" t="n"/>
@@ -1796,7 +1817,7 @@
         </is>
       </c>
       <c r="G21" s="31">
-        <f>SUMIFS('Journal Financier'!$F$5:$F$304,'Journal Financier'!$B$5:$B$304,$G$5,'Journal Financier'!$C$5:$C$304,"Dépense",'Journal Financier'!$D$5:$D$304,"Maintenance",'Journal Financier'!$A$5:$A$304,"&gt;="&amp;$C$6,'Journal Financier'!$A$5:$A$304,"&lt;="&amp;$G$6)</f>
+        <f>SUMIFS('Journal Financier'!$F$5:$F$304,'Journal Financier'!$B$5:$B$304,$G$5,'Journal Financier'!$C$5:$C$304,"Dépense",'Journal Financier'!$D$5:$D$304,"Maintenance",'Journal Financier'!$A$5:$A$304,"&gt;="&amp;IF($C$6="",0,$C$6),'Journal Financier'!$A$5:$A$304,"&lt;="&amp;IF($G$6="",DATE(2099,12,31),$G$6))</f>
         <v/>
       </c>
       <c r="H21" s="40" t="n"/>
@@ -1808,7 +1829,7 @@
         </is>
       </c>
       <c r="G22" s="31">
-        <f>SUMIFS('Journal Financier'!$F$5:$F$304,'Journal Financier'!$B$5:$B$304,$G$5,'Journal Financier'!$C$5:$C$304,"Dépense",'Journal Financier'!$D$5:$D$304,"Consommables",'Journal Financier'!$A$5:$A$304,"&gt;="&amp;$C$6,'Journal Financier'!$A$5:$A$304,"&lt;="&amp;$G$6)</f>
+        <f>SUMIFS('Journal Financier'!$F$5:$F$304,'Journal Financier'!$B$5:$B$304,$G$5,'Journal Financier'!$C$5:$C$304,"Dépense",'Journal Financier'!$D$5:$D$304,"Consommables",'Journal Financier'!$A$5:$A$304,"&gt;="&amp;IF($C$6="",0,$C$6),'Journal Financier'!$A$5:$A$304,"&lt;="&amp;IF($G$6="",DATE(2099,12,31),$G$6))</f>
         <v/>
       </c>
       <c r="H22" s="40" t="n"/>
@@ -1820,7 +1841,7 @@
         </is>
       </c>
       <c r="G23" s="31">
-        <f>SUMIFS('Journal Financier'!$F$5:$F$304,'Journal Financier'!$B$5:$B$304,$G$5,'Journal Financier'!$C$5:$C$304,"Dépense",'Journal Financier'!$D$5:$D$304,"Électricité",'Journal Financier'!$A$5:$A$304,"&gt;="&amp;$C$6,'Journal Financier'!$A$5:$A$304,"&lt;="&amp;$G$6)</f>
+        <f>SUMIFS('Journal Financier'!$F$5:$F$304,'Journal Financier'!$B$5:$B$304,$G$5,'Journal Financier'!$C$5:$C$304,"Dépense",'Journal Financier'!$D$5:$D$304,"Électricité",'Journal Financier'!$A$5:$A$304,"&gt;="&amp;IF($C$6="",0,$C$6),'Journal Financier'!$A$5:$A$304,"&lt;="&amp;IF($G$6="",DATE(2099,12,31),$G$6))</f>
         <v/>
       </c>
       <c r="H23" s="40" t="n"/>
@@ -1832,7 +1853,7 @@
         </is>
       </c>
       <c r="G24" s="31">
-        <f>SUMIFS('Journal Financier'!$F$5:$F$304,'Journal Financier'!$B$5:$B$304,$G$5,'Journal Financier'!$C$5:$C$304,"Dépense",'Journal Financier'!$D$5:$D$304,"Eau",'Journal Financier'!$A$5:$A$304,"&gt;="&amp;$C$6,'Journal Financier'!$A$5:$A$304,"&lt;="&amp;$G$6)</f>
+        <f>SUMIFS('Journal Financier'!$F$5:$F$304,'Journal Financier'!$B$5:$B$304,$G$5,'Journal Financier'!$C$5:$C$304,"Dépense",'Journal Financier'!$D$5:$D$304,"Eau",'Journal Financier'!$A$5:$A$304,"&gt;="&amp;IF($C$6="",0,$C$6),'Journal Financier'!$A$5:$A$304,"&lt;="&amp;IF($G$6="",DATE(2099,12,31),$G$6))</f>
         <v/>
       </c>
       <c r="H24" s="40" t="n"/>
@@ -1844,7 +1865,7 @@
         </is>
       </c>
       <c r="G25" s="31">
-        <f>SUMIFS('Journal Financier'!$F$5:$F$304,'Journal Financier'!$B$5:$B$304,$G$5,'Journal Financier'!$C$5:$C$304,"Dépense",'Journal Financier'!$D$5:$D$304,"Publicité",'Journal Financier'!$A$5:$A$304,"&gt;="&amp;$C$6,'Journal Financier'!$A$5:$A$304,"&lt;="&amp;$G$6)</f>
+        <f>SUMIFS('Journal Financier'!$F$5:$F$304,'Journal Financier'!$B$5:$B$304,$G$5,'Journal Financier'!$C$5:$C$304,"Dépense",'Journal Financier'!$D$5:$D$304,"Publicité",'Journal Financier'!$A$5:$A$304,"&gt;="&amp;IF($C$6="",0,$C$6),'Journal Financier'!$A$5:$A$304,"&lt;="&amp;IF($G$6="",DATE(2099,12,31),$G$6))</f>
         <v/>
       </c>
       <c r="H25" s="40" t="n"/>
@@ -1949,6 +1970,7 @@
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="1" fitToWidth="1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
